--- a/sample.xlsx
+++ b/sample.xlsx
@@ -54,7 +54,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -123,6 +123,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
@@ -132,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -146,7 +161,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -745,17 +763,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Longest Option</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Shortest Option</t>
         </is>
